--- a/Docs/assets to import - final from logistic Burj.xlsx
+++ b/Docs/assets to import - final from logistic Burj.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\logistic\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BB811A-44D3-45DB-AF97-8E01E9BC0FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E77BB0F-0F65-4DB5-82A1-B2B0182C5B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-36" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="109">
   <si>
     <t>Furniture</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>Gaz Heaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owned By </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B&amp;Z </t>
   </si>
 </sst>
 </file>
@@ -832,22 +838,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W174"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X174"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="63.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -917,8 +923,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -984,8 +993,11 @@
         <v>28</v>
       </c>
       <c r="W2" s="2"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1051,8 +1063,11 @@
         <v>28</v>
       </c>
       <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1116,8 +1131,11 @@
         <v>28</v>
       </c>
       <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1181,8 +1199,11 @@
         <v>28</v>
       </c>
       <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1246,8 +1267,11 @@
         <v>28</v>
       </c>
       <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X6" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1311,8 +1335,11 @@
         <v>28</v>
       </c>
       <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X7" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1376,8 +1403,11 @@
         <v>28</v>
       </c>
       <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1441,8 +1471,11 @@
         <v>28</v>
       </c>
       <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1506,8 +1539,11 @@
         <v>28</v>
       </c>
       <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1571,8 +1607,11 @@
         <v>28</v>
       </c>
       <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1636,8 +1675,11 @@
         <v>28</v>
       </c>
       <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1701,8 +1743,11 @@
         <v>28</v>
       </c>
       <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1766,8 +1811,11 @@
         <v>28</v>
       </c>
       <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1831,8 +1879,11 @@
         <v>28</v>
       </c>
       <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X15" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1896,8 +1947,11 @@
         <v>28</v>
       </c>
       <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X16" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1961,8 +2015,11 @@
         <v>28</v>
       </c>
       <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2026,8 +2083,11 @@
         <v>28</v>
       </c>
       <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2091,8 +2151,11 @@
         <v>28</v>
       </c>
       <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2156,8 +2219,11 @@
         <v>28</v>
       </c>
       <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2219,8 +2285,11 @@
         <v>28</v>
       </c>
       <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X21" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2282,8 +2351,11 @@
         <v>28</v>
       </c>
       <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X22" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2345,8 +2417,11 @@
         <v>28</v>
       </c>
       <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X23" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2408,8 +2483,11 @@
         <v>28</v>
       </c>
       <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X24" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2471,8 +2549,11 @@
         <v>28</v>
       </c>
       <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2534,8 +2615,11 @@
         <v>28</v>
       </c>
       <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X26" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2597,8 +2681,11 @@
         <v>28</v>
       </c>
       <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2660,8 +2747,11 @@
         <v>28</v>
       </c>
       <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X28" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2723,8 +2813,11 @@
         <v>28</v>
       </c>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X29" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2788,8 +2881,11 @@
         <v>28</v>
       </c>
       <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X30" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2853,8 +2949,11 @@
         <v>28</v>
       </c>
       <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X31" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2918,8 +3017,11 @@
         <v>28</v>
       </c>
       <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2983,8 +3085,11 @@
         <v>28</v>
       </c>
       <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3048,8 +3153,11 @@
         <v>28</v>
       </c>
       <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X34" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3113,8 +3221,11 @@
         <v>28</v>
       </c>
       <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X35" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3178,8 +3289,11 @@
         <v>28</v>
       </c>
       <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X36" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3243,8 +3357,11 @@
         <v>28</v>
       </c>
       <c r="W37" s="2"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3308,8 +3425,11 @@
         <v>28</v>
       </c>
       <c r="W38" s="2"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X38" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3371,8 +3491,11 @@
         <v>28</v>
       </c>
       <c r="W39" s="2"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X39" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3434,8 +3557,11 @@
         <v>28</v>
       </c>
       <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X40" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3496,8 +3622,11 @@
       <c r="V41" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X41" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3558,8 +3687,11 @@
       <c r="V42" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3620,8 +3752,11 @@
       <c r="V43" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X43" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3682,8 +3817,11 @@
       <c r="V44" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3744,8 +3882,11 @@
       <c r="V45" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X45" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3806,8 +3947,11 @@
       <c r="V46" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X46" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3868,8 +4012,11 @@
       <c r="V47" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X47" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3930,8 +4077,11 @@
       <c r="V48" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3992,8 +4142,11 @@
       <c r="V49" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X49" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4054,8 +4207,11 @@
       <c r="V50" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X50" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4116,8 +4272,11 @@
       <c r="V51" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>83</v>
       </c>
@@ -4180,8 +4339,11 @@
       <c r="V52" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X52" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>84</v>
       </c>
@@ -4242,8 +4404,11 @@
       <c r="V53" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X53" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>85</v>
       </c>
@@ -4304,8 +4469,11 @@
       <c r="V54" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X54" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>86</v>
       </c>
@@ -4368,8 +4536,11 @@
       <c r="V55" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X55" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>87</v>
       </c>
@@ -4432,8 +4603,11 @@
       <c r="V56" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X56" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>88</v>
       </c>
@@ -4497,8 +4671,11 @@
         <v>28</v>
       </c>
       <c r="W57" s="2"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X57" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>89</v>
       </c>
@@ -4562,8 +4739,11 @@
         <v>28</v>
       </c>
       <c r="W58" s="2"/>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X58" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>90</v>
       </c>
@@ -4627,8 +4807,11 @@
         <v>28</v>
       </c>
       <c r="W59" s="2"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X59" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>91</v>
       </c>
@@ -4692,8 +4875,11 @@
         <v>28</v>
       </c>
       <c r="W60" s="2"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>92</v>
       </c>
@@ -4757,8 +4943,11 @@
         <v>28</v>
       </c>
       <c r="W61" s="2"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X61" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>93</v>
       </c>
@@ -4820,8 +5009,11 @@
         <v>28</v>
       </c>
       <c r="W62" s="2"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X62" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>94</v>
       </c>
@@ -4883,8 +5075,11 @@
         <v>28</v>
       </c>
       <c r="W63" s="2"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X63" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>95</v>
       </c>
@@ -4946,8 +5141,11 @@
         <v>28</v>
       </c>
       <c r="W64" s="2"/>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X64" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>96</v>
       </c>
@@ -5009,8 +5207,11 @@
         <v>28</v>
       </c>
       <c r="W65" s="2"/>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X65" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>97</v>
       </c>
@@ -5069,8 +5270,11 @@
         <v>28</v>
       </c>
       <c r="W66" s="2"/>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X66" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>98</v>
       </c>
@@ -5129,8 +5333,11 @@
         <v>28</v>
       </c>
       <c r="W67" s="2"/>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X67" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>99</v>
       </c>
@@ -5189,8 +5396,11 @@
         <v>28</v>
       </c>
       <c r="W68" s="2"/>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X68" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>100</v>
       </c>
@@ -5249,8 +5459,11 @@
         <v>28</v>
       </c>
       <c r="W69" s="2"/>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X69" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>101</v>
       </c>
@@ -5309,8 +5522,11 @@
         <v>28</v>
       </c>
       <c r="W70" s="2"/>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X70" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>102</v>
       </c>
@@ -5369,8 +5585,11 @@
         <v>28</v>
       </c>
       <c r="W71" s="2"/>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X71" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>103</v>
       </c>
@@ -5429,8 +5648,11 @@
         <v>28</v>
       </c>
       <c r="W72" s="2"/>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X72" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>104</v>
       </c>
@@ -5489,8 +5711,11 @@
         <v>28</v>
       </c>
       <c r="W73" s="2"/>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X73" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>105</v>
       </c>
@@ -5549,8 +5774,11 @@
         <v>28</v>
       </c>
       <c r="W74" s="2"/>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X74" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>106</v>
       </c>
@@ -5609,8 +5837,11 @@
         <v>28</v>
       </c>
       <c r="W75" s="2"/>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X75" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>107</v>
       </c>
@@ -5669,8 +5900,11 @@
         <v>28</v>
       </c>
       <c r="W76" s="2"/>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X76" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>108</v>
       </c>
@@ -5732,8 +5966,11 @@
         <v>28</v>
       </c>
       <c r="W77" s="2"/>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X77" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>109</v>
       </c>
@@ -5797,8 +6034,11 @@
         <v>28</v>
       </c>
       <c r="W78" s="2"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X78" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>110</v>
       </c>
@@ -5862,8 +6102,11 @@
         <v>28</v>
       </c>
       <c r="W79" s="2"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X79" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>111</v>
       </c>
@@ -5927,8 +6170,11 @@
         <v>28</v>
       </c>
       <c r="W80" s="2"/>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X80" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>112</v>
       </c>
@@ -5992,8 +6238,11 @@
         <v>28</v>
       </c>
       <c r="W81" s="2"/>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X81" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>113</v>
       </c>
@@ -6057,8 +6306,11 @@
         <v>28</v>
       </c>
       <c r="W82" s="2"/>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X82" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>114</v>
       </c>
@@ -6122,8 +6374,11 @@
         <v>28</v>
       </c>
       <c r="W83" s="2"/>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X83" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>120</v>
       </c>
@@ -6189,8 +6444,11 @@
         <v>28</v>
       </c>
       <c r="W84" s="2"/>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X84" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>121</v>
       </c>
@@ -6254,8 +6512,11 @@
         <v>28</v>
       </c>
       <c r="W85" s="2"/>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X85" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>122</v>
       </c>
@@ -6319,8 +6580,11 @@
         <v>28</v>
       </c>
       <c r="W86" s="2"/>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X86" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>123</v>
       </c>
@@ -6384,8 +6648,11 @@
         <v>28</v>
       </c>
       <c r="W87" s="2"/>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X87" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>124</v>
       </c>
@@ -6449,8 +6716,11 @@
         <v>28</v>
       </c>
       <c r="W88" s="2"/>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X88" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>125</v>
       </c>
@@ -6514,8 +6784,11 @@
         <v>28</v>
       </c>
       <c r="W89" s="2"/>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X89" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>126</v>
       </c>
@@ -6579,8 +6852,11 @@
         <v>28</v>
       </c>
       <c r="W90" s="2"/>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X90" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>129</v>
       </c>
@@ -6641,8 +6917,11 @@
         <v>28</v>
       </c>
       <c r="W91" s="2"/>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X91" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>131</v>
       </c>
@@ -6704,8 +6983,11 @@
         <v>28</v>
       </c>
       <c r="W92" s="2"/>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X92" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>132</v>
       </c>
@@ -6767,8 +7049,11 @@
         <v>28</v>
       </c>
       <c r="W93" s="2"/>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X93" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>133</v>
       </c>
@@ -6830,8 +7115,11 @@
         <v>28</v>
       </c>
       <c r="W94" s="2"/>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X94" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>134</v>
       </c>
@@ -6893,8 +7181,11 @@
         <v>28</v>
       </c>
       <c r="W95" s="2"/>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X95" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>135</v>
       </c>
@@ -6956,8 +7247,11 @@
         <v>28</v>
       </c>
       <c r="W96" s="2"/>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X96" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>136</v>
       </c>
@@ -7019,8 +7313,11 @@
         <v>28</v>
       </c>
       <c r="W97" s="2"/>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X97" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K98" s="6"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -7034,8 +7331,9 @@
       <c r="U98" s="2"/>
       <c r="V98" s="2"/>
       <c r="W98" s="2"/>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X98" s="2"/>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K99" s="6"/>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -7049,8 +7347,9 @@
       <c r="U99" s="2"/>
       <c r="V99" s="2"/>
       <c r="W99" s="2"/>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X99" s="2"/>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K100" s="6"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -7064,8 +7363,9 @@
       <c r="U100" s="2"/>
       <c r="V100" s="2"/>
       <c r="W100" s="2"/>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X100" s="2"/>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K101" s="6"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -7079,8 +7379,9 @@
       <c r="U101" s="2"/>
       <c r="V101" s="2"/>
       <c r="W101" s="2"/>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X101" s="2"/>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K102" s="6"/>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -7094,7 +7395,7 @@
       <c r="U102" s="2"/>
       <c r="W102" s="2"/>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K103" s="6"/>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -7108,8 +7409,9 @@
       <c r="U103" s="2"/>
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X103" s="2"/>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K104" s="6"/>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -7123,8 +7425,9 @@
       <c r="U104" s="2"/>
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X104" s="2"/>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K105" s="6"/>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -7138,8 +7441,9 @@
       <c r="U105" s="2"/>
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X105" s="2"/>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K106" s="6"/>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -7153,8 +7457,9 @@
       <c r="U106" s="2"/>
       <c r="V106" s="2"/>
       <c r="W106" s="2"/>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X106" s="2"/>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K107" s="6"/>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -7168,8 +7473,9 @@
       <c r="U107" s="2"/>
       <c r="V107" s="2"/>
       <c r="W107" s="2"/>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X107" s="2"/>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K108" s="6"/>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -7183,8 +7489,9 @@
       <c r="U108" s="2"/>
       <c r="V108" s="2"/>
       <c r="W108" s="2"/>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X108" s="2"/>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K109" s="6"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -7198,8 +7505,9 @@
       <c r="U109" s="2"/>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X109" s="2"/>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K110" s="6"/>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -7213,7 +7521,7 @@
       <c r="U110" s="2"/>
       <c r="W110" s="2"/>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K111" s="6"/>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -7227,8 +7535,9 @@
       <c r="U111" s="2"/>
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X111" s="2"/>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K112" s="6"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -7242,8 +7551,9 @@
       <c r="U112" s="2"/>
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
-    </row>
-    <row r="113" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X112" s="2"/>
+    </row>
+    <row r="113" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K113" s="6"/>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -7257,8 +7567,9 @@
       <c r="U113" s="2"/>
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
-    </row>
-    <row r="114" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X113" s="2"/>
+    </row>
+    <row r="114" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K114" s="6"/>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -7272,8 +7583,9 @@
       <c r="U114" s="2"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-    </row>
-    <row r="115" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X114" s="2"/>
+    </row>
+    <row r="115" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K115" s="6"/>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -7287,8 +7599,9 @@
       <c r="U115" s="2"/>
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
-    </row>
-    <row r="116" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X115" s="2"/>
+    </row>
+    <row r="116" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K116" s="6"/>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -7302,8 +7615,9 @@
       <c r="U116" s="2"/>
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
-    </row>
-    <row r="117" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X116" s="2"/>
+    </row>
+    <row r="117" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K117" s="6"/>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -7317,8 +7631,9 @@
       <c r="U117" s="2"/>
       <c r="V117" s="2"/>
       <c r="W117" s="2"/>
-    </row>
-    <row r="118" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X117" s="2"/>
+    </row>
+    <row r="118" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K118" s="6"/>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -7332,7 +7647,7 @@
       <c r="U118" s="2"/>
       <c r="W118" s="2"/>
     </row>
-    <row r="119" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K119" s="6"/>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -7346,7 +7661,7 @@
       <c r="U119" s="2"/>
       <c r="W119" s="2"/>
     </row>
-    <row r="120" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K120" s="6"/>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -7359,8 +7674,9 @@
       <c r="U120" s="2"/>
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
-    </row>
-    <row r="121" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X120" s="2"/>
+    </row>
+    <row r="121" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K121" s="6"/>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -7374,8 +7690,9 @@
       <c r="U121" s="2"/>
       <c r="V121" s="2"/>
       <c r="W121" s="2"/>
-    </row>
-    <row r="122" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X121" s="2"/>
+    </row>
+    <row r="122" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K122" s="6"/>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -7389,8 +7706,9 @@
       <c r="U122" s="2"/>
       <c r="V122" s="2"/>
       <c r="W122" s="2"/>
-    </row>
-    <row r="123" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X122" s="2"/>
+    </row>
+    <row r="123" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K123" s="6"/>
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
@@ -7404,8 +7722,9 @@
       <c r="U123" s="2"/>
       <c r="V123" s="2"/>
       <c r="W123" s="2"/>
-    </row>
-    <row r="124" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X123" s="2"/>
+    </row>
+    <row r="124" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K124" s="6"/>
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
@@ -7419,8 +7738,9 @@
       <c r="U124" s="2"/>
       <c r="V124" s="2"/>
       <c r="W124" s="2"/>
-    </row>
-    <row r="125" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X124" s="2"/>
+    </row>
+    <row r="125" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K125" s="6"/>
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
@@ -7434,8 +7754,9 @@
       <c r="U125" s="2"/>
       <c r="V125" s="2"/>
       <c r="W125" s="2"/>
-    </row>
-    <row r="126" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X125" s="2"/>
+    </row>
+    <row r="126" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K126" s="6"/>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
@@ -7449,7 +7770,7 @@
       <c r="U126" s="2"/>
       <c r="W126" s="2"/>
     </row>
-    <row r="127" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K127" s="6"/>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -7463,7 +7784,7 @@
       <c r="U127" s="2"/>
       <c r="W127" s="2"/>
     </row>
-    <row r="128" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K128" s="6"/>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -7477,7 +7798,7 @@
       <c r="U128" s="2"/>
       <c r="W128" s="2"/>
     </row>
-    <row r="129" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K129" s="6"/>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -7491,7 +7812,7 @@
       <c r="U129" s="2"/>
       <c r="W129" s="2"/>
     </row>
-    <row r="130" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K130" s="6"/>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -7505,7 +7826,7 @@
       <c r="U130" s="2"/>
       <c r="W130" s="2"/>
     </row>
-    <row r="131" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K131" s="6"/>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -7519,7 +7840,7 @@
       <c r="U131" s="2"/>
       <c r="W131" s="2"/>
     </row>
-    <row r="132" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K132" s="6"/>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -7533,8 +7854,9 @@
       <c r="U132" s="2"/>
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
-    </row>
-    <row r="133" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X132" s="2"/>
+    </row>
+    <row r="133" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K133" s="6"/>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -7548,8 +7870,9 @@
       <c r="U133" s="2"/>
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
-    </row>
-    <row r="134" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X133" s="2"/>
+    </row>
+    <row r="134" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K134" s="6"/>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -7563,8 +7886,9 @@
       <c r="U134" s="2"/>
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
-    </row>
-    <row r="135" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X134" s="2"/>
+    </row>
+    <row r="135" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K135" s="6"/>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -7578,8 +7902,9 @@
       <c r="U135" s="2"/>
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
-    </row>
-    <row r="136" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X135" s="2"/>
+    </row>
+    <row r="136" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K136" s="6"/>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -7593,8 +7918,9 @@
       <c r="U136" s="2"/>
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
-    </row>
-    <row r="137" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X136" s="2"/>
+    </row>
+    <row r="137" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K137" s="5"/>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -7608,7 +7934,7 @@
       <c r="U137" s="2"/>
       <c r="W137" s="2"/>
     </row>
-    <row r="138" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K138" s="5"/>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -7622,7 +7948,7 @@
       <c r="U138" s="2"/>
       <c r="W138" s="2"/>
     </row>
-    <row r="139" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K139" s="5"/>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -7636,7 +7962,7 @@
       <c r="U139" s="2"/>
       <c r="W139" s="2"/>
     </row>
-    <row r="140" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K140" s="5"/>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -7650,7 +7976,7 @@
       <c r="U140" s="2"/>
       <c r="W140" s="2"/>
     </row>
-    <row r="141" spans="11:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K141" s="5"/>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -7664,8 +7990,9 @@
       <c r="U141" s="2"/>
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
-    </row>
-    <row r="142" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X141" s="2"/>
+    </row>
+    <row r="142" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K142" s="5"/>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -7679,8 +8006,9 @@
       <c r="U142" s="2"/>
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
-    </row>
-    <row r="143" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X142" s="2"/>
+    </row>
+    <row r="143" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K143" s="5"/>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -7694,8 +8022,9 @@
       <c r="U143" s="2"/>
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
-    </row>
-    <row r="144" spans="11:23" x14ac:dyDescent="0.25">
+      <c r="X143" s="2"/>
+    </row>
+    <row r="144" spans="11:24" x14ac:dyDescent="0.3">
       <c r="K144" s="5"/>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -7709,8 +8038,9 @@
       <c r="U144" s="2"/>
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
-    </row>
-    <row r="145" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X144" s="2"/>
+    </row>
+    <row r="145" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K145" s="5"/>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -7724,8 +8054,9 @@
       <c r="U145" s="2"/>
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
-    </row>
-    <row r="146" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X145" s="2"/>
+    </row>
+    <row r="146" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K146" s="5"/>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -7739,8 +8070,9 @@
       <c r="U146" s="2"/>
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
-    </row>
-    <row r="147" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X146" s="2"/>
+    </row>
+    <row r="147" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K147" s="5"/>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -7754,7 +8086,7 @@
       <c r="U147" s="2"/>
       <c r="W147" s="2"/>
     </row>
-    <row r="148" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K148" s="5"/>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -7768,7 +8100,7 @@
       <c r="U148" s="2"/>
       <c r="W148" s="2"/>
     </row>
-    <row r="149" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K149" s="5"/>
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
@@ -7782,7 +8114,7 @@
       <c r="U149" s="2"/>
       <c r="W149" s="2"/>
     </row>
-    <row r="150" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K150" s="5"/>
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
@@ -7796,7 +8128,7 @@
       <c r="U150" s="2"/>
       <c r="W150" s="2"/>
     </row>
-    <row r="151" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K151" s="5"/>
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
@@ -7810,8 +8142,9 @@
       <c r="U151" s="2"/>
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
-    </row>
-    <row r="152" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X151" s="2"/>
+    </row>
+    <row r="152" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K152" s="5"/>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -7825,8 +8158,9 @@
       <c r="U152" s="2"/>
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
-    </row>
-    <row r="153" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X152" s="2"/>
+    </row>
+    <row r="153" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K153" s="5"/>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -7840,8 +8174,9 @@
       <c r="U153" s="2"/>
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
-    </row>
-    <row r="154" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X153" s="2"/>
+    </row>
+    <row r="154" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K154" s="5"/>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -7855,8 +8190,9 @@
       <c r="U154" s="2"/>
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
-    </row>
-    <row r="155" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X154" s="2"/>
+    </row>
+    <row r="155" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K155" s="5"/>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -7870,8 +8206,9 @@
       <c r="U155" s="2"/>
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
-    </row>
-    <row r="156" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X155" s="2"/>
+    </row>
+    <row r="156" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K156" s="5"/>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -7885,8 +8222,9 @@
       <c r="U156" s="2"/>
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
-    </row>
-    <row r="157" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X156" s="2"/>
+    </row>
+    <row r="157" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K157" s="5"/>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -7900,8 +8238,9 @@
       <c r="U157" s="2"/>
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
-    </row>
-    <row r="158" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X157" s="2"/>
+    </row>
+    <row r="158" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K158" s="5"/>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -7915,8 +8254,9 @@
       <c r="U158" s="2"/>
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
-    </row>
-    <row r="159" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X158" s="2"/>
+    </row>
+    <row r="159" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K159" s="5"/>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -7930,7 +8270,7 @@
       <c r="U159" s="2"/>
       <c r="W159" s="2"/>
     </row>
-    <row r="160" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
@@ -7949,7 +8289,7 @@
       <c r="U160" s="7"/>
       <c r="W160" s="7"/>
     </row>
-    <row r="161" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
@@ -7968,7 +8308,7 @@
       <c r="U161" s="7"/>
       <c r="W161" s="7"/>
     </row>
-    <row r="162" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K162" s="5"/>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -7982,7 +8322,7 @@
       <c r="U162" s="2"/>
       <c r="W162" s="7"/>
     </row>
-    <row r="163" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K163" s="5"/>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -7996,7 +8336,7 @@
       <c r="U163" s="2"/>
       <c r="W163" s="7"/>
     </row>
-    <row r="164" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K164" s="5"/>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -8010,7 +8350,7 @@
       <c r="U164" s="2"/>
       <c r="W164" s="7"/>
     </row>
-    <row r="165" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K165" s="5"/>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -8024,8 +8364,9 @@
       <c r="U165" s="2"/>
       <c r="V165" s="2"/>
       <c r="W165" s="7"/>
-    </row>
-    <row r="166" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X165" s="2"/>
+    </row>
+    <row r="166" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K166" s="5"/>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -8039,8 +8380,9 @@
       <c r="U166" s="2"/>
       <c r="V166" s="2"/>
       <c r="W166" s="7"/>
-    </row>
-    <row r="167" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X166" s="2"/>
+    </row>
+    <row r="167" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K167" s="5"/>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -8054,7 +8396,7 @@
       <c r="U167" s="2"/>
       <c r="W167" s="7"/>
     </row>
-    <row r="168" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K168" s="5"/>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -8068,7 +8410,7 @@
       <c r="U168" s="2"/>
       <c r="W168" s="7"/>
     </row>
-    <row r="169" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K169" s="5"/>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -8082,7 +8424,7 @@
       <c r="U169" s="2"/>
       <c r="W169" s="7"/>
     </row>
-    <row r="170" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K170" s="5"/>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -8096,7 +8438,7 @@
       <c r="U170" s="2"/>
       <c r="W170" s="7"/>
     </row>
-    <row r="171" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K171" s="5"/>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
@@ -8110,7 +8452,7 @@
       <c r="U171" s="2"/>
       <c r="W171" s="7"/>
     </row>
-    <row r="172" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K172" s="5"/>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
@@ -8124,7 +8466,7 @@
       <c r="U172" s="2"/>
       <c r="W172" s="7"/>
     </row>
-    <row r="173" spans="3:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K173" s="5"/>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -8138,8 +8480,9 @@
       <c r="U173" s="2"/>
       <c r="V173" s="2"/>
       <c r="W173" s="7"/>
-    </row>
-    <row r="174" spans="3:23" x14ac:dyDescent="0.25">
+      <c r="X173" s="2"/>
+    </row>
+    <row r="174" spans="3:24" x14ac:dyDescent="0.3">
       <c r="K174" s="5"/>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -8153,10 +8496,11 @@
       <c r="U174" s="2"/>
       <c r="V174" s="2"/>
       <c r="W174" s="7"/>
+      <c r="X174" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G10:G18 G20:G174 G2:G8" xr:uid="{58155949-CB1B-48D8-A226-133575A9F708}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
     </dataValidation>
@@ -8172,6 +8516,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C174" xr:uid="{C310BEFD-AB98-4273-AFFC-E63848748976}">
       <formula1>Category</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X97" xr:uid="{84E55D4F-C737-4B08-B138-B34DFBBB9491}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8179,23 +8526,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFFF102-26E2-4B46-85F9-06F0C3E86F0F}">
-  <dimension ref="A1:W48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:X48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" customWidth="1"/>
+    <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -8265,8 +8613,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>51</v>
       </c>
@@ -8330,8 +8681,11 @@
         <v>28</v>
       </c>
       <c r="W2" s="2"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>52</v>
       </c>
@@ -8395,8 +8749,11 @@
         <v>28</v>
       </c>
       <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>53</v>
       </c>
@@ -8460,8 +8817,11 @@
         <v>28</v>
       </c>
       <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>54</v>
       </c>
@@ -8525,8 +8885,11 @@
         <v>28</v>
       </c>
       <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>55</v>
       </c>
@@ -8590,8 +8953,11 @@
         <v>28</v>
       </c>
       <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X6" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>56</v>
       </c>
@@ -8655,8 +9021,11 @@
         <v>28</v>
       </c>
       <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X7" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>57</v>
       </c>
@@ -8720,8 +9089,11 @@
         <v>28</v>
       </c>
       <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>58</v>
       </c>
@@ -8785,8 +9157,11 @@
         <v>28</v>
       </c>
       <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>59</v>
       </c>
@@ -8850,8 +9225,11 @@
         <v>28</v>
       </c>
       <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>60</v>
       </c>
@@ -8914,8 +9292,11 @@
       <c r="V11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>61</v>
       </c>
@@ -8979,8 +9360,11 @@
         <v>28</v>
       </c>
       <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>62</v>
       </c>
@@ -9044,8 +9428,11 @@
         <v>28</v>
       </c>
       <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>63</v>
       </c>
@@ -9109,8 +9496,11 @@
         <v>28</v>
       </c>
       <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>64</v>
       </c>
@@ -9174,8 +9564,11 @@
         <v>28</v>
       </c>
       <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X15" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>65</v>
       </c>
@@ -9239,8 +9632,11 @@
         <v>28</v>
       </c>
       <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X16" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>66</v>
       </c>
@@ -9304,8 +9700,11 @@
         <v>28</v>
       </c>
       <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>67</v>
       </c>
@@ -9369,8 +9768,11 @@
         <v>28</v>
       </c>
       <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>68</v>
       </c>
@@ -9434,8 +9836,11 @@
         <v>28</v>
       </c>
       <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>69</v>
       </c>
@@ -9499,8 +9904,11 @@
         <v>28</v>
       </c>
       <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>70</v>
       </c>
@@ -9564,8 +9972,11 @@
         <v>28</v>
       </c>
       <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>71</v>
       </c>
@@ -9629,8 +10040,11 @@
         <v>28</v>
       </c>
       <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X22" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>72</v>
       </c>
@@ -9694,8 +10108,11 @@
         <v>28</v>
       </c>
       <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X23" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>73</v>
       </c>
@@ -9759,8 +10176,11 @@
         <v>28</v>
       </c>
       <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X24" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>74</v>
       </c>
@@ -9824,8 +10244,11 @@
         <v>28</v>
       </c>
       <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>75</v>
       </c>
@@ -9889,8 +10312,11 @@
         <v>28</v>
       </c>
       <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X26" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>76</v>
       </c>
@@ -9954,8 +10380,11 @@
         <v>28</v>
       </c>
       <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>77</v>
       </c>
@@ -10019,8 +10448,11 @@
         <v>28</v>
       </c>
       <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>78</v>
       </c>
@@ -10084,8 +10516,11 @@
         <v>28</v>
       </c>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X29" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>79</v>
       </c>
@@ -10149,8 +10584,11 @@
         <v>28</v>
       </c>
       <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X30" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>80</v>
       </c>
@@ -10214,8 +10652,11 @@
         <v>28</v>
       </c>
       <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X31" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>81</v>
       </c>
@@ -10279,8 +10720,11 @@
         <v>28</v>
       </c>
       <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X32" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>82</v>
       </c>
@@ -10344,8 +10788,11 @@
         <v>28</v>
       </c>
       <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>115</v>
       </c>
@@ -10409,8 +10856,11 @@
         <v>28</v>
       </c>
       <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X34" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>116</v>
       </c>
@@ -10474,8 +10924,11 @@
         <v>28</v>
       </c>
       <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X35" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>117</v>
       </c>
@@ -10539,8 +10992,11 @@
         <v>28</v>
       </c>
       <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X36" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>118</v>
       </c>
@@ -10604,8 +11060,11 @@
         <v>28</v>
       </c>
       <c r="W37" s="2"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>119</v>
       </c>
@@ -10669,8 +11128,11 @@
         <v>28</v>
       </c>
       <c r="W38" s="2"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X38" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>127</v>
       </c>
@@ -10732,8 +11194,11 @@
         <v>28</v>
       </c>
       <c r="W39" s="2"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X39" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>128</v>
       </c>
@@ -10795,8 +11260,11 @@
         <v>28</v>
       </c>
       <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X40" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>130</v>
       </c>
@@ -10858,8 +11326,11 @@
         <v>28</v>
       </c>
       <c r="W41" s="2"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X41" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K42" s="5"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -10873,8 +11344,9 @@
       <c r="U42" s="2"/>
       <c r="V42" s="2"/>
       <c r="W42" s="2"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X42" s="2"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B43" s="15"/>
       <c r="K43" s="6"/>
       <c r="L43" s="2"/>
@@ -10888,8 +11360,9 @@
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X43" s="2"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K44" s="5"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -10903,8 +11376,9 @@
       <c r="U44" s="2"/>
       <c r="V44" s="2"/>
       <c r="W44" s="7"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X44" s="2"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K45" s="5"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -10918,8 +11392,9 @@
       <c r="U45" s="2"/>
       <c r="V45" s="2"/>
       <c r="W45" s="7"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X45" s="2"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K46" s="5"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -10932,7 +11407,7 @@
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K47" s="6"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -10944,8 +11419,9 @@
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
       <c r="V47" s="2"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X47" s="2"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K48" s="6"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -10958,10 +11434,11 @@
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
       <c r="V48" s="2"/>
+      <c r="X48" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W48" xr:uid="{7AFFF102-26E2-4B46-85F9-06F0C3E86F0F}"/>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11 F2:F48" xr:uid="{EFD74BD8-58C9-4ACB-93B3-5302AF9CB479}">
       <formula1>INDIRECT(D2&amp;"_material")</formula1>
     </dataValidation>
@@ -10974,6 +11451,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C48" xr:uid="{BF2AFAAE-B6D2-412A-B5FA-591E8B15DA0C}">
       <formula1>Category</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X41" xr:uid="{0EA251FD-FFB7-44C7-9832-FB9A7CF2D147}">
+      <formula1>"LandLord , B&amp;Z "</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -10983,22 +11463,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087FDD54-5E17-401C-A88E-55822B904567}">
   <dimension ref="A1:X6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -11069,7 +11549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="I2" s="8"/>
       <c r="K2" s="6"/>
@@ -11087,7 +11567,7 @@
       <c r="W2" s="2"/>
       <c r="X2" s="16"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
       <c r="K3" s="6"/>
       <c r="M3" s="2"/>
@@ -11102,7 +11582,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -11122,7 +11602,7 @@
       <c r="U4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K5" s="5"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -11137,7 +11617,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="K6" s="6"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -11174,16 +11654,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45841932-2100-4D5F-A69E-818128AA5E3E}">
   <dimension ref="A1:AA4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -11266,20 +11746,20 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G2" s="11"/>
       <c r="I2" s="9"/>
       <c r="T2" s="8"/>
       <c r="X2" s="2"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G3" s="11"/>
       <c r="I3" s="9"/>
       <c r="O3" s="18"/>
       <c r="T3" s="8"/>
       <c r="X3" s="2"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G4" s="11"/>
       <c r="I4" s="9"/>
       <c r="T4" s="8"/>
@@ -11310,18 +11790,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E46FE8D-6B9D-4019-AD13-4A9515E01ECE}">
   <dimension ref="A1:T18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" customWidth="1"/>
     <col min="19" max="19" width="55" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -11383,16 +11863,16 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B7" s="14"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P9" s="8"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="P16" s="8"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="14"/>
       <c r="J18" s="19"/>
     </row>
@@ -11415,14 +11895,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB899B9E-9D29-4608-AC57-3843A909BED5}">
   <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -11492,15 +11972,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D0FD15-6627-45B8-AE32-055E4B703EE2}">
   <dimension ref="A1:T1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
